--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-GEM-ERPCHRG-PR-Communication-ChargChangeReq.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-GEM-ERPCHRG-PR-Communication-ChargChangeReq.xlsx
@@ -1126,7 +1126,7 @@
     <t>Communication.recipient.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-telematik-id}
+    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-telematik-id}
 </t>
   </si>
   <si>
@@ -1161,7 +1161,7 @@
     <t>Communication.sender.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-kvid-10}
+    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-kvid-10}
 </t>
   </si>
   <si>

--- a/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-GEM-ERPCHRG-PR-Communication-ChargChangeReq.xlsx
+++ b/eflow-chargeitem/build/1.1.0-draft/StructureDefinition-GEM-ERPCHRG-PR-Communication-ChargChangeReq.xlsx
@@ -1126,7 +1126,7 @@
     <t>Communication.recipient.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-telematik-id}
+    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-telematik-id}
 </t>
   </si>
   <si>
@@ -1161,7 +1161,7 @@
     <t>Communication.sender.identifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {https://gematik.de/fhir/erpchrg/StructureDefinition/identifier-kvid-10}
+    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-kvid-10}
 </t>
   </si>
   <si>
